--- a/artfynd/Lillgoberget artfynd.xlsx
+++ b/artfynd/Lillgoberget artfynd.xlsx
@@ -3407,7 +3407,7 @@
         <v>126864684</v>
       </c>
       <c r="B29" t="n">
-        <v>78730</v>
+        <v>78774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>122746387</v>
       </c>
       <c r="B70" t="n">
-        <v>92127</v>
+        <v>92593</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>122746373</v>
       </c>
       <c r="B73" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>122746375</v>
       </c>
       <c r="B80" t="n">
-        <v>91924</v>
+        <v>91985</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>122746377</v>
       </c>
       <c r="B104" t="n">
-        <v>91876</v>
+        <v>91937</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>122745910</v>
       </c>
       <c r="B121" t="n">
-        <v>80434</v>
+        <v>80488</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>122746378</v>
       </c>
       <c r="B122" t="n">
-        <v>80434</v>
+        <v>80488</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>122745909</v>
       </c>
       <c r="B137" t="n">
-        <v>80463</v>
+        <v>80493</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>122745907</v>
       </c>
       <c r="B164" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>122745908</v>
       </c>
       <c r="B165" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>122745912</v>
       </c>
       <c r="B166" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>122746371</v>
       </c>
       <c r="B167" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>122746372</v>
       </c>
       <c r="B168" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>122746374</v>
       </c>
       <c r="B169" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>122746379</v>
       </c>
       <c r="B170" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>122746380</v>
       </c>
       <c r="B171" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>122746381</v>
       </c>
       <c r="B172" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>122746382</v>
       </c>
       <c r="B173" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>122746383</v>
       </c>
       <c r="B174" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>122746385</v>
       </c>
       <c r="B175" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>122746386</v>
       </c>
       <c r="B176" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>122746388</v>
       </c>
       <c r="B177" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>122746389</v>
       </c>
       <c r="B178" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>122746390</v>
       </c>
       <c r="B179" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>122746391</v>
       </c>
       <c r="B180" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>122746392</v>
       </c>
       <c r="B181" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>122746393</v>
       </c>
       <c r="B182" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>122746395</v>
       </c>
       <c r="B183" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>122746396</v>
       </c>
       <c r="B184" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>122746409</v>
       </c>
       <c r="B243" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>122746410</v>
       </c>
       <c r="B244" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>122746404</v>
       </c>
       <c r="B253" t="n">
-        <v>91924</v>
+        <v>91985</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>122746403</v>
       </c>
       <c r="B263" t="n">
-        <v>91876</v>
+        <v>91937</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>122746369</v>
       </c>
       <c r="B265" t="n">
-        <v>79329</v>
+        <v>79373</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>122746398</v>
       </c>
       <c r="B286" t="n">
-        <v>80434</v>
+        <v>80488</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>122746368</v>
       </c>
       <c r="B315" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>122746370</v>
       </c>
       <c r="B316" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>122746397</v>
       </c>
       <c r="B317" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>122746399</v>
       </c>
       <c r="B318" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>122746401</v>
       </c>
       <c r="B319" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>122746402</v>
       </c>
       <c r="B320" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>122746406</v>
       </c>
       <c r="B372" t="n">
-        <v>99144</v>
+        <v>99217</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
